--- a/outputs/Block6C_Close_Race_Risk.xlsx
+++ b/outputs/Block6C_Close_Race_Risk.xlsx
@@ -417,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>19.13</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,7 +425,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>31.37</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>46.3</v>
+        <v>55.76</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -441,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>70.84</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -449,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>67.73</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -457,7 +457,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>19.32</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -465,7 +465,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>10.94</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>77.45999999999999</v>
+        <v>56.96</v>
       </c>
     </row>
   </sheetData>
